--- a/lecNote/09_Project/etc/프로젝트관리.xlsx
+++ b/lecNote/09_Project/etc/프로젝트관리.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ai\lecNote\09_Project\etc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai\lecNote\09_Project\etc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F920F348-9B06-4C76-B1CF-F844C86A22CC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC158FC9-EFD5-4E97-8A82-7C1DE46B9738}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23145" yWindow="-60" windowWidth="23250" windowHeight="14010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>기획 및 설계</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -107,10 +107,6 @@
   </si>
   <si>
     <t>전반</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>계획</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -160,6 +156,22 @@
   </si>
   <si>
     <t>9/23(수)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김길동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박길동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>윤길동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홍길동</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -244,7 +256,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -290,6 +302,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF66"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -449,7 +479,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -528,41 +558,50 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -600,6 +639,7 @@
   </tableStyles>
   <colors>
     <mruColors>
+      <color rgb="FFFFFF66"/>
       <color rgb="FFFFFFCC"/>
       <color rgb="FFFFFFFF"/>
       <color rgb="FFE1FFE1"/>
@@ -609,7 +649,6 @@
       <color rgb="FFE5F4F7"/>
       <color rgb="FFCCFFCC"/>
       <color rgb="FFCCFFFF"/>
-      <color rgb="FFFFFF99"/>
     </mruColors>
   </colors>
   <extLst>
@@ -959,41 +998,41 @@
     <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
+      <c r="B2" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
@@ -1038,65 +1077,65 @@
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="12"/>
       <c r="B6" s="16"/>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="29" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="21"/>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="36" t="s">
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
-      <c r="O6" s="35"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
       <c r="P6" s="17"/>
       <c r="Q6" s="2"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="12"/>
       <c r="B7" s="9"/>
-      <c r="C7" s="34"/>
+      <c r="C7" s="30"/>
       <c r="D7" s="18"/>
       <c r="E7" s="24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F7" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="H7" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="I7" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="J7" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="J7" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" s="25" t="s">
+      <c r="L7" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="L7" s="25" t="s">
+      <c r="M7" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="N7" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="N7" s="25" t="s">
+      <c r="O7" s="25" t="s">
         <v>31</v>
-      </c>
-      <c r="O7" s="25" t="s">
-        <v>32</v>
       </c>
       <c r="P7" s="19"/>
       <c r="Q7" s="2"/>
@@ -1163,7 +1202,7 @@
     <row r="11" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="33" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="6"/>
@@ -1184,7 +1223,7 @@
     <row r="12" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="37"/>
+      <c r="C12" s="33"/>
       <c r="D12" s="6"/>
       <c r="E12" s="4"/>
       <c r="F12" s="2"/>
@@ -1222,7 +1261,7 @@
     <row r="14" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="2"/>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="26" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="6"/>
@@ -1243,7 +1282,7 @@
     <row r="15" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="2"/>
-      <c r="C15" s="30"/>
+      <c r="C15" s="26"/>
       <c r="D15" s="6"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -1302,12 +1341,12 @@
     <row r="18" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="2"/>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="35" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="20"/>
+      <c r="F18" s="40"/>
       <c r="G18" s="20"/>
       <c r="H18" s="20"/>
       <c r="I18" s="20"/>
@@ -1323,7 +1362,7 @@
     <row r="19" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="2"/>
-      <c r="C19" s="28"/>
+      <c r="C19" s="35"/>
       <c r="D19" s="6"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
@@ -1361,7 +1400,7 @@
     <row r="21" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12"/>
       <c r="B21" s="2"/>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="35" t="s">
         <v>10</v>
       </c>
       <c r="D21" s="6"/>
@@ -1382,7 +1421,7 @@
     <row r="22" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12"/>
       <c r="B22" s="2"/>
-      <c r="C22" s="28"/>
+      <c r="C22" s="35"/>
       <c r="D22" s="6"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -1420,7 +1459,7 @@
     <row r="24" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="35" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="6"/>
@@ -1441,7 +1480,7 @@
     <row r="25" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12"/>
       <c r="B25" s="2"/>
-      <c r="C25" s="28"/>
+      <c r="C25" s="35"/>
       <c r="D25" s="6"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
@@ -1479,7 +1518,7 @@
     <row r="27" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="12"/>
       <c r="B27" s="2"/>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="35" t="s">
         <v>5</v>
       </c>
       <c r="D27" s="6"/>
@@ -1500,7 +1539,7 @@
     <row r="28" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="12"/>
       <c r="B28" s="2"/>
-      <c r="C28" s="28"/>
+      <c r="C28" s="35"/>
       <c r="D28" s="6"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
@@ -1559,7 +1598,7 @@
     <row r="31" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="12"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="29" t="s">
+      <c r="C31" s="36" t="s">
         <v>12</v>
       </c>
       <c r="D31" s="6"/>
@@ -1580,7 +1619,7 @@
     <row r="32" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="12"/>
       <c r="B32" s="2"/>
-      <c r="C32" s="29"/>
+      <c r="C32" s="36"/>
       <c r="D32" s="6"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -1618,7 +1657,7 @@
     <row r="34" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="12"/>
       <c r="B34" s="2"/>
-      <c r="C34" s="29" t="s">
+      <c r="C34" s="36" t="s">
         <v>13</v>
       </c>
       <c r="D34" s="6"/>
@@ -1639,7 +1678,7 @@
     <row r="35" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="12"/>
       <c r="B35" s="2"/>
-      <c r="C35" s="29"/>
+      <c r="C35" s="36"/>
       <c r="D35" s="6"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
@@ -1698,7 +1737,7 @@
     <row r="38" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12"/>
       <c r="B38" s="2"/>
-      <c r="C38" s="26" t="s">
+      <c r="C38" s="34" t="s">
         <v>14</v>
       </c>
       <c r="D38" s="6"/>
@@ -1719,7 +1758,7 @@
     <row r="39" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="12"/>
       <c r="B39" s="2"/>
-      <c r="C39" s="26"/>
+      <c r="C39" s="34"/>
       <c r="D39" s="6"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
@@ -1757,7 +1796,7 @@
     <row r="41" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="12"/>
       <c r="B41" s="2"/>
-      <c r="C41" s="26" t="s">
+      <c r="C41" s="34" t="s">
         <v>17</v>
       </c>
       <c r="D41" s="6"/>
@@ -1778,7 +1817,7 @@
     <row r="42" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="12"/>
       <c r="B42" s="2"/>
-      <c r="C42" s="26"/>
+      <c r="C42" s="34"/>
       <c r="D42" s="6"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
@@ -1816,7 +1855,7 @@
     <row r="44" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="12"/>
       <c r="B44" s="2"/>
-      <c r="C44" s="26" t="s">
+      <c r="C44" s="34" t="s">
         <v>18</v>
       </c>
       <c r="D44" s="6"/>
@@ -1837,7 +1876,7 @@
     <row r="45" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="12"/>
       <c r="B45" s="2"/>
-      <c r="C45" s="26"/>
+      <c r="C45" s="34"/>
       <c r="D45" s="6"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
@@ -1875,7 +1914,7 @@
     <row r="47" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="12"/>
       <c r="B47" s="2"/>
-      <c r="C47" s="26" t="s">
+      <c r="C47" s="34" t="s">
         <v>19</v>
       </c>
       <c r="D47" s="6"/>
@@ -1896,7 +1935,7 @@
     <row r="48" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="12"/>
       <c r="B48" s="2"/>
-      <c r="C48" s="26"/>
+      <c r="C48" s="34"/>
       <c r="D48" s="6"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
@@ -1934,7 +1973,7 @@
     <row r="50" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="12"/>
       <c r="B50" s="2"/>
-      <c r="C50" s="26" t="s">
+      <c r="C50" s="34" t="s">
         <v>16</v>
       </c>
       <c r="D50" s="6"/>
@@ -1955,7 +1994,7 @@
     <row r="51" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="12"/>
       <c r="B51" s="2"/>
-      <c r="C51" s="26"/>
+      <c r="C51" s="34"/>
       <c r="D51" s="6"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -1993,7 +2032,7 @@
     <row r="53" spans="1:17" ht="6.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="12"/>
       <c r="B53" s="2"/>
-      <c r="C53" s="27" t="s">
+      <c r="C53" s="37" t="s">
         <v>15</v>
       </c>
       <c r="D53" s="3"/>
@@ -2014,7 +2053,7 @@
     <row r="54" spans="1:17" ht="6.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="12"/>
       <c r="B54" s="2"/>
-      <c r="C54" s="27"/>
+      <c r="C54" s="37"/>
       <c r="D54" s="3"/>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
@@ -2078,9 +2117,17 @@
       <c r="G57" s="23"/>
       <c r="H57" s="23"/>
       <c r="I57" s="23"/>
-      <c r="M57" s="2"/>
-      <c r="N57" s="20" t="s">
-        <v>22</v>
+      <c r="K57" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="L57" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="M57" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="N57" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="O57" s="22" t="s">
         <v>2</v>
@@ -2108,12 +2155,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B2:O3"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="E6:J6"/>
-    <mergeCell ref="K6:O6"/>
-    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="C53:C54"/>
     <mergeCell ref="C38:C39"/>
     <mergeCell ref="C18:C19"/>
     <mergeCell ref="C21:C22"/>
@@ -2121,11 +2167,12 @@
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="C31:C32"/>
     <mergeCell ref="C34:C35"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B2:O3"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="E6:J6"/>
+    <mergeCell ref="K6:O6"/>
+    <mergeCell ref="C11:C12"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/lecNote/09_Project/etc/프로젝트관리.xlsx
+++ b/lecNote/09_Project/etc/프로젝트관리.xlsx
@@ -8,23 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai\lecNote\09_Project\etc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC158FC9-EFD5-4E97-8A82-7C1DE46B9738}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1700DABF-B1C7-482D-8EE1-3EFAA3EE07F0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23145" yWindow="-60" windowWidth="23250" windowHeight="14010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gantt Chart" sheetId="8" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="179021"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
-  <si>
-    <t>기획 및 설계</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>활동내용</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -38,38 +34,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>설계, 기능정의, 데이터수집</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이론적 배경</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>서론 및 이론적 배경</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>연구 모형 및 조사 설계</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>실증 분석 및 결론</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>연구 배경 및 목적</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>연구 내용 및 방법</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>프로젝트의 구성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>연구모형 및 연구가설</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -78,75 +42,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>자료 수집 및 표본의 특성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트 및 수정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 분석 및 시각화</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>측정항목의 기술통계분석 및 시각화</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>신뢰도 및 타당성 검증 및 시각화</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>각자에 맞는 데이터분석 및 시각화</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>후반</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>전반</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1/18(토)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1/14(화)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1/15(수)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1/16(목)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1/17(금)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1/20(월)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1/21(화)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1/22(수)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1/23(목)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1/24(금)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -172,6 +72,118 @@
   </si>
   <si>
     <t>홍길동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9/28(월)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9/29(화)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9/30(수)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/1(목)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/3(토)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/4(일)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/5(월)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/6(화)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/8(목)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/2(금)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/7(수)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/9(금)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/10(일)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주제선정 및 기획초안 작성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터 전처리 및 인사이트 도출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI 모델링 및 테스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>웹페이지 개발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터베이스 모델링 및 최적화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UML 작성(시나리오 및 플로우 설계)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>웹 대시보드 및 화면 개발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예측 서비스 기능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회원관리 기능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트 및 발표 자료 제작</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설계, 기능정의, 기획초안 작성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공공데이터 포털 데이터 정리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xxx 데이터 수집/ooo크롤링</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그룹화 분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시각화</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -558,6 +570,15 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -593,15 +614,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -983,60 +995,66 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:T58"/>
   <sheetFormatPr defaultColWidth="2.25" defaultRowHeight="11.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.25" style="1"/>
     <col min="2" max="2" width="0.625" style="1" customWidth="1"/>
     <col min="3" max="3" width="26.75" style="1" customWidth="1"/>
     <col min="4" max="4" width="0.75" style="1" customWidth="1"/>
-    <col min="5" max="15" width="5.25" style="1" customWidth="1"/>
-    <col min="16" max="16" width="0.75" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="2.25" style="1"/>
+    <col min="5" max="18" width="5.25" style="1" customWidth="1"/>
+    <col min="19" max="19" width="0.75" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="2.25" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B2" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-    </row>
-    <row r="4" spans="1:17" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
+      <c r="Q3" s="31"/>
+      <c r="R3" s="31"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+    </row>
+    <row r="4" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -1052,10 +1070,13 @@
       <c r="M4" s="10"/>
       <c r="N4" s="10"/>
       <c r="O4" s="10"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="2"/>
-    </row>
-    <row r="5" spans="1:17" ht="4.1500000000000004" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="2"/>
+    </row>
+    <row r="5" spans="1:20" ht="4.1500000000000004" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -1071,76 +1092,91 @@
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="2"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="2"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="12"/>
       <c r="B6" s="16"/>
-      <c r="C6" s="29" t="s">
-        <v>1</v>
+      <c r="C6" s="32" t="s">
+        <v>0</v>
       </c>
       <c r="D6" s="21"/>
-      <c r="E6" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="31"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="2"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E6" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="M6" s="34"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="34"/>
+      <c r="P6" s="34"/>
+      <c r="Q6" s="34"/>
+      <c r="R6" s="34"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="2"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="12"/>
       <c r="B7" s="9"/>
-      <c r="C7" s="30"/>
+      <c r="C7" s="33"/>
       <c r="D7" s="18"/>
       <c r="E7" s="24" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J7" s="25" t="s">
         <v>22</v>
       </c>
       <c r="K7" s="25" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="L7" s="25" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="M7" s="25" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="N7" s="25" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O7" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="P7" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q7" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="R7" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="S7" s="19"/>
+      <c r="T7" s="2"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="12"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1156,14 +1192,17 @@
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="12"/>
+      <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
-    </row>
-    <row r="9" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R8" s="2"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="2"/>
+    </row>
+    <row r="9" spans="1:20" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="2"/>
       <c r="C9" s="8" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="2"/>
@@ -1177,10 +1216,13 @@
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="12"/>
+      <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
-    </row>
-    <row r="10" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R9" s="2"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="2"/>
+    </row>
+    <row r="10" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="2"/>
       <c r="C10" s="5"/>
@@ -1196,14 +1238,17 @@
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="12"/>
+      <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
-    </row>
-    <row r="11" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R10" s="2"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="2"/>
+    </row>
+    <row r="11" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="33" t="s">
-        <v>3</v>
+      <c r="C11" s="36" t="s">
+        <v>2</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="20"/>
@@ -1217,13 +1262,16 @@
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-      <c r="P11" s="12"/>
+      <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
-    </row>
-    <row r="12" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R11" s="2"/>
+      <c r="S11" s="12"/>
+      <c r="T11" s="2"/>
+    </row>
+    <row r="12" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="33"/>
+      <c r="C12" s="36"/>
       <c r="D12" s="6"/>
       <c r="E12" s="4"/>
       <c r="F12" s="2"/>
@@ -1236,10 +1284,13 @@
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-      <c r="P12" s="12"/>
+      <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
-    </row>
-    <row r="13" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R12" s="2"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="2"/>
+    </row>
+    <row r="13" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="2"/>
       <c r="C13" s="6"/>
@@ -1255,14 +1306,17 @@
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
-      <c r="P13" s="12"/>
+      <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
-    </row>
-    <row r="14" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R13" s="2"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="2"/>
+    </row>
+    <row r="14" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="2"/>
-      <c r="C14" s="26" t="s">
-        <v>4</v>
+      <c r="C14" s="29" t="s">
+        <v>36</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="20"/>
@@ -1276,13 +1330,16 @@
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
-      <c r="P14" s="12"/>
+      <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
-    </row>
-    <row r="15" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R14" s="2"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="2"/>
+    </row>
+    <row r="15" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="2"/>
-      <c r="C15" s="26"/>
+      <c r="C15" s="29"/>
       <c r="D15" s="6"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -1295,10 +1352,13 @@
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
-      <c r="P15" s="12"/>
+      <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
-    </row>
-    <row r="16" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R15" s="2"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="2"/>
+    </row>
+    <row r="16" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="2"/>
       <c r="C16" s="6"/>
@@ -1314,14 +1374,17 @@
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
-      <c r="P16" s="12"/>
+      <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
-    </row>
-    <row r="17" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R16" s="2"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="2"/>
+    </row>
+    <row r="17" spans="1:20" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="2"/>
       <c r="C17" s="9" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -1335,34 +1398,40 @@
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
-      <c r="P17" s="12"/>
+      <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
-    </row>
-    <row r="18" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R17" s="2"/>
+      <c r="S17" s="12"/>
+      <c r="T17" s="2"/>
+    </row>
+    <row r="18" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="2"/>
-      <c r="C18" s="35" t="s">
-        <v>9</v>
+      <c r="C18" s="38" t="s">
+        <v>38</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="40"/>
+      <c r="F18" s="28"/>
       <c r="G18" s="20"/>
       <c r="H18" s="20"/>
       <c r="I18" s="20"/>
       <c r="J18" s="20"/>
-      <c r="K18" s="2"/>
+      <c r="K18" s="20"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
-      <c r="P18" s="12"/>
+      <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
-    </row>
-    <row r="19" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R18" s="2"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="2"/>
+    </row>
+    <row r="19" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="2"/>
-      <c r="C19" s="35"/>
+      <c r="C19" s="38"/>
       <c r="D19" s="6"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
@@ -1375,10 +1444,13 @@
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
-      <c r="P19" s="12"/>
+      <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
-    </row>
-    <row r="20" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R19" s="2"/>
+      <c r="S19" s="12"/>
+      <c r="T19" s="2"/>
+    </row>
+    <row r="20" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12"/>
       <c r="B20" s="2"/>
       <c r="C20" s="6"/>
@@ -1394,14 +1466,17 @@
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
-      <c r="P20" s="12"/>
+      <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
-    </row>
-    <row r="21" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R20" s="2"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="2"/>
+    </row>
+    <row r="21" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12"/>
       <c r="B21" s="2"/>
-      <c r="C21" s="35" t="s">
-        <v>10</v>
+      <c r="C21" s="38" t="s">
+        <v>37</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="2"/>
@@ -1409,19 +1484,22 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="20"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
-      <c r="P21" s="12"/>
+      <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
-    </row>
-    <row r="22" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R21" s="2"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="2"/>
+    </row>
+    <row r="22" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12"/>
       <c r="B22" s="2"/>
-      <c r="C22" s="35"/>
+      <c r="C22" s="38"/>
       <c r="D22" s="6"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -1434,10 +1512,13 @@
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-      <c r="P22" s="12"/>
+      <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
-    </row>
-    <row r="23" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R22" s="2"/>
+      <c r="S22" s="12"/>
+      <c r="T22" s="2"/>
+    </row>
+    <row r="23" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" s="2"/>
       <c r="C23" s="6"/>
@@ -1453,14 +1534,17 @@
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
-      <c r="P23" s="12"/>
+      <c r="P23" s="2"/>
       <c r="Q23" s="2"/>
-    </row>
-    <row r="24" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R23" s="2"/>
+      <c r="S23" s="12"/>
+      <c r="T23" s="2"/>
+    </row>
+    <row r="24" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="35" t="s">
-        <v>11</v>
+      <c r="C24" s="38" t="s">
+        <v>39</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="2"/>
@@ -1468,19 +1552,22 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="20"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
-      <c r="P24" s="12"/>
+      <c r="P24" s="2"/>
       <c r="Q24" s="2"/>
-    </row>
-    <row r="25" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R24" s="2"/>
+      <c r="S24" s="12"/>
+      <c r="T24" s="2"/>
+    </row>
+    <row r="25" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12"/>
       <c r="B25" s="2"/>
-      <c r="C25" s="35"/>
+      <c r="C25" s="38"/>
       <c r="D25" s="6"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
@@ -1492,11 +1579,14 @@
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="12"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
-    </row>
-    <row r="26" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R25" s="7"/>
+      <c r="S25" s="12"/>
+      <c r="T25" s="2"/>
+    </row>
+    <row r="26" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12"/>
       <c r="B26" s="2"/>
       <c r="C26" s="6"/>
@@ -1512,14 +1602,17 @@
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
-      <c r="P26" s="12"/>
+      <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
-    </row>
-    <row r="27" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R26" s="2"/>
+      <c r="S26" s="12"/>
+      <c r="T26" s="2"/>
+    </row>
+    <row r="27" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="12"/>
       <c r="B27" s="2"/>
-      <c r="C27" s="35" t="s">
-        <v>5</v>
+      <c r="C27" s="38" t="s">
+        <v>40</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="2"/>
@@ -1527,19 +1620,22 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="20"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
-      <c r="P27" s="12"/>
+      <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
-    </row>
-    <row r="28" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R27" s="2"/>
+      <c r="S27" s="12"/>
+      <c r="T27" s="2"/>
+    </row>
+    <row r="28" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="12"/>
       <c r="B28" s="2"/>
-      <c r="C28" s="35"/>
+      <c r="C28" s="38"/>
       <c r="D28" s="6"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
@@ -1552,10 +1648,13 @@
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
-      <c r="P28" s="12"/>
+      <c r="P28" s="2"/>
       <c r="Q28" s="2"/>
-    </row>
-    <row r="29" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R28" s="2"/>
+      <c r="S28" s="12"/>
+      <c r="T28" s="2"/>
+    </row>
+    <row r="29" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="12"/>
       <c r="B29" s="2"/>
       <c r="C29" s="6"/>
@@ -1571,14 +1670,17 @@
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
-      <c r="P29" s="12"/>
+      <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
-    </row>
-    <row r="30" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R29" s="2"/>
+      <c r="S29" s="12"/>
+      <c r="T29" s="2"/>
+    </row>
+    <row r="30" spans="1:20" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="12"/>
       <c r="B30" s="2"/>
       <c r="C30" s="9" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -1592,14 +1694,17 @@
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
-      <c r="P30" s="12"/>
+      <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
-    </row>
-    <row r="31" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R30" s="2"/>
+      <c r="S30" s="12"/>
+      <c r="T30" s="2"/>
+    </row>
+    <row r="31" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="12"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="36" t="s">
-        <v>12</v>
+      <c r="C31" s="39" t="s">
+        <v>3</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="2"/>
@@ -1608,18 +1713,21 @@
       <c r="H31" s="20"/>
       <c r="I31" s="20"/>
       <c r="J31" s="20"/>
-      <c r="K31" s="2"/>
+      <c r="K31" s="20"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
-      <c r="P31" s="12"/>
+      <c r="P31" s="2"/>
       <c r="Q31" s="2"/>
-    </row>
-    <row r="32" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R31" s="2"/>
+      <c r="S31" s="12"/>
+      <c r="T31" s="2"/>
+    </row>
+    <row r="32" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="12"/>
       <c r="B32" s="2"/>
-      <c r="C32" s="36"/>
+      <c r="C32" s="39"/>
       <c r="D32" s="6"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -1632,10 +1740,13 @@
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
-      <c r="P32" s="12"/>
+      <c r="P32" s="2"/>
       <c r="Q32" s="2"/>
-    </row>
-    <row r="33" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R32" s="2"/>
+      <c r="S32" s="12"/>
+      <c r="T32" s="2"/>
+    </row>
+    <row r="33" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="12"/>
       <c r="B33" s="2"/>
       <c r="C33" s="6"/>
@@ -1651,14 +1762,17 @@
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
-      <c r="P33" s="12"/>
+      <c r="P33" s="2"/>
       <c r="Q33" s="2"/>
-    </row>
-    <row r="34" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R33" s="2"/>
+      <c r="S33" s="12"/>
+      <c r="T33" s="2"/>
+    </row>
+    <row r="34" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="12"/>
       <c r="B34" s="2"/>
-      <c r="C34" s="36" t="s">
-        <v>13</v>
+      <c r="C34" s="39" t="s">
+        <v>4</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="2"/>
@@ -1667,18 +1781,21 @@
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
-      <c r="K34" s="20"/>
+      <c r="K34" s="2"/>
       <c r="L34" s="20"/>
       <c r="M34" s="20"/>
       <c r="N34" s="20"/>
-      <c r="O34" s="2"/>
-      <c r="P34" s="12"/>
-      <c r="Q34" s="2"/>
-    </row>
-    <row r="35" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O34" s="20"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="20"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="12"/>
+      <c r="T34" s="2"/>
+    </row>
+    <row r="35" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="12"/>
       <c r="B35" s="2"/>
-      <c r="C35" s="36"/>
+      <c r="C35" s="39"/>
       <c r="D35" s="6"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
@@ -1691,10 +1808,13 @@
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
-      <c r="P35" s="12"/>
+      <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
-    </row>
-    <row r="36" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R35" s="2"/>
+      <c r="S35" s="12"/>
+      <c r="T35" s="2"/>
+    </row>
+    <row r="36" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="12"/>
       <c r="B36" s="2"/>
       <c r="C36" s="6"/>
@@ -1710,14 +1830,17 @@
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
-      <c r="P36" s="12"/>
+      <c r="P36" s="2"/>
       <c r="Q36" s="2"/>
-    </row>
-    <row r="37" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R36" s="2"/>
+      <c r="S36" s="12"/>
+      <c r="T36" s="2"/>
+    </row>
+    <row r="37" spans="1:20" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="12"/>
       <c r="B37" s="2"/>
       <c r="C37" s="9" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -1731,14 +1854,17 @@
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
-      <c r="P37" s="12"/>
+      <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
-    </row>
-    <row r="38" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R37" s="2"/>
+      <c r="S37" s="12"/>
+      <c r="T37" s="2"/>
+    </row>
+    <row r="38" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12"/>
       <c r="B38" s="2"/>
-      <c r="C38" s="34" t="s">
-        <v>14</v>
+      <c r="C38" s="37" t="s">
+        <v>30</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="2"/>
@@ -1747,18 +1873,21 @@
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
-      <c r="K38" s="20"/>
+      <c r="K38" s="2"/>
       <c r="L38" s="20"/>
       <c r="M38" s="20"/>
       <c r="N38" s="20"/>
-      <c r="O38" s="2"/>
-      <c r="P38" s="12"/>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O38" s="20"/>
+      <c r="P38" s="20"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="12"/>
+      <c r="T38" s="2"/>
+    </row>
+    <row r="39" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="12"/>
       <c r="B39" s="2"/>
-      <c r="C39" s="34"/>
+      <c r="C39" s="37"/>
       <c r="D39" s="6"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
@@ -1771,10 +1900,13 @@
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
-      <c r="P39" s="12"/>
+      <c r="P39" s="2"/>
       <c r="Q39" s="2"/>
-    </row>
-    <row r="40" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R39" s="2"/>
+      <c r="S39" s="12"/>
+      <c r="T39" s="2"/>
+    </row>
+    <row r="40" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="12"/>
       <c r="B40" s="2"/>
       <c r="C40" s="6"/>
@@ -1790,14 +1922,17 @@
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
-      <c r="P40" s="12"/>
+      <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
-    </row>
-    <row r="41" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R40" s="2"/>
+      <c r="S40" s="12"/>
+      <c r="T40" s="2"/>
+    </row>
+    <row r="41" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="12"/>
       <c r="B41" s="2"/>
-      <c r="C41" s="34" t="s">
-        <v>17</v>
+      <c r="C41" s="37" t="s">
+        <v>31</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="2"/>
@@ -1806,18 +1941,21 @@
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
-      <c r="K41" s="20"/>
+      <c r="K41" s="2"/>
       <c r="L41" s="20"/>
       <c r="M41" s="20"/>
       <c r="N41" s="20"/>
-      <c r="O41" s="2"/>
-      <c r="P41" s="12"/>
-      <c r="Q41" s="2"/>
-    </row>
-    <row r="42" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O41" s="20"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="20"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="12"/>
+      <c r="T41" s="2"/>
+    </row>
+    <row r="42" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="12"/>
       <c r="B42" s="2"/>
-      <c r="C42" s="34"/>
+      <c r="C42" s="37"/>
       <c r="D42" s="6"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
@@ -1830,10 +1968,13 @@
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
-      <c r="P42" s="12"/>
+      <c r="P42" s="2"/>
       <c r="Q42" s="2"/>
-    </row>
-    <row r="43" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R42" s="2"/>
+      <c r="S42" s="12"/>
+      <c r="T42" s="2"/>
+    </row>
+    <row r="43" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="12"/>
       <c r="B43" s="2"/>
       <c r="C43" s="6"/>
@@ -1849,14 +1990,17 @@
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
-      <c r="P43" s="12"/>
+      <c r="P43" s="2"/>
       <c r="Q43" s="2"/>
-    </row>
-    <row r="44" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R43" s="2"/>
+      <c r="S43" s="12"/>
+      <c r="T43" s="2"/>
+    </row>
+    <row r="44" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="12"/>
       <c r="B44" s="2"/>
-      <c r="C44" s="34" t="s">
-        <v>18</v>
+      <c r="C44" s="37" t="s">
+        <v>32</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="2"/>
@@ -1865,18 +2009,21 @@
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
-      <c r="K44" s="20"/>
+      <c r="K44" s="2"/>
       <c r="L44" s="20"/>
       <c r="M44" s="20"/>
       <c r="N44" s="20"/>
-      <c r="O44" s="2"/>
-      <c r="P44" s="12"/>
-      <c r="Q44" s="2"/>
-    </row>
-    <row r="45" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O44" s="20"/>
+      <c r="P44" s="20"/>
+      <c r="Q44" s="20"/>
+      <c r="R44" s="2"/>
+      <c r="S44" s="12"/>
+      <c r="T44" s="2"/>
+    </row>
+    <row r="45" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="12"/>
       <c r="B45" s="2"/>
-      <c r="C45" s="34"/>
+      <c r="C45" s="37"/>
       <c r="D45" s="6"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
@@ -1889,10 +2036,13 @@
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
-      <c r="P45" s="12"/>
+      <c r="P45" s="2"/>
       <c r="Q45" s="2"/>
-    </row>
-    <row r="46" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R45" s="2"/>
+      <c r="S45" s="12"/>
+      <c r="T45" s="2"/>
+    </row>
+    <row r="46" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="12"/>
       <c r="B46" s="2"/>
       <c r="C46" s="6"/>
@@ -1908,14 +2058,17 @@
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
-      <c r="P46" s="12"/>
+      <c r="P46" s="2"/>
       <c r="Q46" s="2"/>
-    </row>
-    <row r="47" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R46" s="2"/>
+      <c r="S46" s="12"/>
+      <c r="T46" s="2"/>
+    </row>
+    <row r="47" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="12"/>
       <c r="B47" s="2"/>
-      <c r="C47" s="34" t="s">
-        <v>19</v>
+      <c r="C47" s="37" t="s">
+        <v>34</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="2"/>
@@ -1923,19 +2076,22 @@
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
-      <c r="J47" s="20"/>
-      <c r="K47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="20"/>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
-      <c r="P47" s="12"/>
+      <c r="P47" s="2"/>
       <c r="Q47" s="2"/>
-    </row>
-    <row r="48" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R47" s="2"/>
+      <c r="S47" s="12"/>
+      <c r="T47" s="2"/>
+    </row>
+    <row r="48" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="12"/>
       <c r="B48" s="2"/>
-      <c r="C48" s="34"/>
+      <c r="C48" s="37"/>
       <c r="D48" s="6"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
@@ -1948,10 +2104,13 @@
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
-      <c r="P48" s="12"/>
+      <c r="P48" s="2"/>
       <c r="Q48" s="2"/>
-    </row>
-    <row r="49" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R48" s="2"/>
+      <c r="S48" s="12"/>
+      <c r="T48" s="2"/>
+    </row>
+    <row r="49" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="12"/>
       <c r="B49" s="2"/>
       <c r="C49" s="6"/>
@@ -1967,14 +2126,17 @@
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
-      <c r="P49" s="12"/>
+      <c r="P49" s="2"/>
       <c r="Q49" s="2"/>
-    </row>
-    <row r="50" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R49" s="2"/>
+      <c r="S49" s="12"/>
+      <c r="T49" s="2"/>
+    </row>
+    <row r="50" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="12"/>
       <c r="B50" s="2"/>
-      <c r="C50" s="34" t="s">
-        <v>16</v>
+      <c r="C50" s="37" t="s">
+        <v>33</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="2"/>
@@ -1982,19 +2144,22 @@
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
-      <c r="J50" s="20"/>
-      <c r="K50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="20"/>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
-      <c r="P50" s="12"/>
+      <c r="P50" s="2"/>
       <c r="Q50" s="2"/>
-    </row>
-    <row r="51" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R50" s="2"/>
+      <c r="S50" s="12"/>
+      <c r="T50" s="2"/>
+    </row>
+    <row r="51" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="12"/>
       <c r="B51" s="2"/>
-      <c r="C51" s="34"/>
+      <c r="C51" s="37"/>
       <c r="D51" s="6"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -2007,10 +2172,13 @@
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
-      <c r="P51" s="12"/>
+      <c r="P51" s="2"/>
       <c r="Q51" s="2"/>
-    </row>
-    <row r="52" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R51" s="2"/>
+      <c r="S51" s="12"/>
+      <c r="T51" s="2"/>
+    </row>
+    <row r="52" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="12"/>
       <c r="B52" s="2"/>
       <c r="C52" s="6"/>
@@ -2026,14 +2194,17 @@
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
-      <c r="P52" s="12"/>
+      <c r="P52" s="2"/>
       <c r="Q52" s="2"/>
-    </row>
-    <row r="53" spans="1:17" ht="6.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R52" s="2"/>
+      <c r="S52" s="12"/>
+      <c r="T52" s="2"/>
+    </row>
+    <row r="53" spans="1:20" ht="6.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="12"/>
       <c r="B53" s="2"/>
-      <c r="C53" s="37" t="s">
-        <v>15</v>
+      <c r="C53" s="40" t="s">
+        <v>35</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="2"/>
@@ -2047,13 +2218,16 @@
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
-      <c r="P53" s="12"/>
+      <c r="P53" s="2"/>
       <c r="Q53" s="2"/>
-    </row>
-    <row r="54" spans="1:17" ht="6.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R53" s="2"/>
+      <c r="S53" s="12"/>
+      <c r="T53" s="2"/>
+    </row>
+    <row r="54" spans="1:20" ht="6.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="12"/>
       <c r="B54" s="2"/>
-      <c r="C54" s="37"/>
+      <c r="C54" s="40"/>
       <c r="D54" s="3"/>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
@@ -2066,10 +2240,13 @@
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
-      <c r="P54" s="12"/>
+      <c r="P54" s="2"/>
       <c r="Q54" s="2"/>
-    </row>
-    <row r="55" spans="1:17" ht="3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R54" s="2"/>
+      <c r="S54" s="12"/>
+      <c r="T54" s="2"/>
+    </row>
+    <row r="55" spans="1:20" ht="3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="12"/>
       <c r="B55" s="13"/>
       <c r="C55" s="11"/>
@@ -2085,10 +2262,13 @@
       <c r="M55" s="11"/>
       <c r="N55" s="11"/>
       <c r="O55" s="11"/>
-      <c r="P55" s="14"/>
-      <c r="Q55" s="2"/>
-    </row>
-    <row r="56" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P55" s="11"/>
+      <c r="Q55" s="11"/>
+      <c r="R55" s="11"/>
+      <c r="S55" s="14"/>
+      <c r="T55" s="2"/>
+    </row>
+    <row r="56" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -2106,8 +2286,11 @@
       <c r="O56" s="2"/>
       <c r="P56" s="2"/>
       <c r="Q56" s="2"/>
-    </row>
-    <row r="57" spans="1:17" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R56" s="2"/>
+      <c r="S56" s="2"/>
+      <c r="T56" s="2"/>
+    </row>
+    <row r="57" spans="1:20" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -2117,25 +2300,28 @@
       <c r="G57" s="23"/>
       <c r="H57" s="23"/>
       <c r="I57" s="23"/>
-      <c r="K57" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="L57" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="M57" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="N57" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="O57" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="P57" s="2"/>
-      <c r="Q57" s="2"/>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="J57" s="23"/>
+      <c r="L57" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="M57" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="N57" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="O57" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="P57" s="27"/>
+      <c r="Q57" s="27"/>
+      <c r="R57" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="S57" s="2"/>
+      <c r="T57" s="2"/>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -2152,6 +2338,9 @@
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" s="2"/>
+      <c r="Q58" s="2"/>
+      <c r="R58" s="2"/>
+      <c r="S58" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -2168,10 +2357,10 @@
     <mergeCell ref="C31:C32"/>
     <mergeCell ref="C34:C35"/>
     <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B2:O3"/>
+    <mergeCell ref="B2:R3"/>
     <mergeCell ref="C6:C7"/>
-    <mergeCell ref="E6:J6"/>
-    <mergeCell ref="K6:O6"/>
+    <mergeCell ref="E6:K6"/>
+    <mergeCell ref="L6:R6"/>
     <mergeCell ref="C11:C12"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/lecNote/09_Project/etc/프로젝트관리.xlsx
+++ b/lecNote/09_Project/etc/프로젝트관리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai\lecNote\09_Project\etc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1700DABF-B1C7-482D-8EE1-3EFAA3EE07F0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF9E356-52B3-4723-BB7A-E6F77413E52E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23145" yWindow="-60" windowWidth="23250" windowHeight="14010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1341,7 +1341,7 @@
       <c r="B15" s="2"/>
       <c r="C15" s="29"/>
       <c r="D15" s="6"/>
-      <c r="E15" s="2"/>
+      <c r="E15" s="26"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -1434,11 +1434,11 @@
       <c r="C19" s="38"/>
       <c r="D19" s="6"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
